--- a/퍼블리싱 일정관리_0917.xlsx
+++ b/퍼블리싱 일정관리_0917.xlsx
@@ -4490,14 +4490,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1973929</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>103790</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5611,7 +5611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="9" customHeight="1" hidden="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" t="s" s="4">
         <v>12</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="9" customHeight="1" hidden="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" t="s" s="4">
         <v>12</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="9" customHeight="1" hidden="1">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" t="s" s="4">
         <v>12</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" ht="9" customHeight="1" hidden="1">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" t="s" s="4">
         <v>34</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" ht="9" customHeight="1" hidden="1">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" t="s" s="4">
         <v>34</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" ht="9" customHeight="1" hidden="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" t="s" s="4">
         <v>34</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" ht="9" customHeight="1" hidden="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" t="s" s="4">
         <v>34</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="9" customHeight="1" hidden="1">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" t="s" s="4">
         <v>34</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="9" customHeight="1" hidden="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" t="s" s="4">
         <v>34</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="9" customHeight="1" hidden="1">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" t="s" s="4">
         <v>34</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" ht="9" customHeight="1" hidden="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" t="s" s="4">
         <v>34</v>
       </c>
@@ -6097,7 +6097,7 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" ht="9" customHeight="1" hidden="1">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" t="s" s="4">
         <v>56</v>
       </c>
@@ -6169,7 +6169,7 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" ht="9" customHeight="1" hidden="1">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" t="s" s="4">
         <v>12</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" ht="9" customHeight="1" hidden="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" t="s" s="4">
         <v>12</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" ht="9" customHeight="1" hidden="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" t="s" s="4">
         <v>12</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="9" customHeight="1" hidden="1">
+    <row r="20" ht="16" customHeight="1">
       <c r="A20" t="s" s="4">
         <v>56</v>
       </c>
@@ -6355,7 +6355,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" ht="9" customHeight="1" hidden="1">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" t="s" s="4">
         <v>56</v>
       </c>
@@ -6461,7 +6461,7 @@
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" ht="9" customHeight="1" hidden="1">
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" t="s" s="4">
         <v>12</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="9" customHeight="1" hidden="1">
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" t="s" s="4">
         <v>56</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" ht="9" customHeight="1" hidden="1">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" t="s" s="4">
         <v>56</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" ht="9" customHeight="1" hidden="1">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" t="s" s="4">
         <v>56</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" ht="9" customHeight="1" hidden="1">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" t="s" s="4">
         <v>56</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="9" customHeight="1" hidden="1">
+    <row r="30" ht="16" customHeight="1">
       <c r="A30" t="s" s="4">
         <v>56</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" ht="9" customHeight="1" hidden="1">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" t="s" s="4">
         <v>12</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" ht="9" customHeight="1" hidden="1">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" t="s" s="4">
         <v>12</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" ht="9" customHeight="1" hidden="1">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" t="s" s="4">
         <v>12</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" ht="9" customHeight="1" hidden="1">
+    <row r="34" ht="16" customHeight="1">
       <c r="A34" t="s" s="4">
         <v>12</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" ht="9" customHeight="1" hidden="1">
+    <row r="35" ht="16" customHeight="1">
       <c r="A35" t="s" s="4">
         <v>12</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" ht="9" customHeight="1" hidden="1">
+    <row r="36" ht="16" customHeight="1">
       <c r="A36" t="s" s="4">
         <v>12</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" ht="9" customHeight="1" hidden="1">
+    <row r="37" ht="16" customHeight="1">
       <c r="A37" t="s" s="4">
         <v>12</v>
       </c>
@@ -6955,7 +6955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" ht="9" customHeight="1" hidden="1">
+    <row r="38" ht="16" customHeight="1">
       <c r="A38" t="s" s="4">
         <v>12</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" ht="9" customHeight="1" hidden="1">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" t="s" s="4">
         <v>34</v>
       </c>
@@ -7065,7 +7065,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" ht="9" customHeight="1" hidden="1">
+    <row r="41" ht="16" customHeight="1">
       <c r="A41" t="s" s="4">
         <v>34</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="42" ht="9" customHeight="1" hidden="1">
+    <row r="42" ht="16" customHeight="1">
       <c r="A42" t="s" s="4">
         <v>56</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" ht="9" customHeight="1" hidden="1">
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" t="s" s="4">
         <v>56</v>
       </c>
@@ -7213,7 +7213,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" ht="9" customHeight="1" hidden="1">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" t="s" s="4">
         <v>12</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" ht="9" customHeight="1" hidden="1">
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" t="s" s="4">
         <v>56</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="47" ht="9" customHeight="1" hidden="1">
+    <row r="47" ht="16" customHeight="1">
       <c r="A47" t="s" s="4">
         <v>56</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" ht="9" customHeight="1" hidden="1">
+    <row r="48" ht="16" customHeight="1">
       <c r="A48" t="s" s="4">
         <v>56</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="49" ht="9" customHeight="1" hidden="1">
+    <row r="49" ht="16" customHeight="1">
       <c r="A49" t="s" s="4">
         <v>56</v>
       </c>
@@ -7437,7 +7437,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" ht="9" customHeight="1" hidden="1">
+    <row r="51" ht="16" customHeight="1">
       <c r="A51" t="s" s="4">
         <v>12</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" ht="9" customHeight="1" hidden="1">
+    <row r="52" ht="16" customHeight="1">
       <c r="A52" t="s" s="4">
         <v>56</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" ht="9" customHeight="1" hidden="1">
+    <row r="53" ht="16" customHeight="1">
       <c r="A53" t="s" s="4">
         <v>56</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="54" ht="9" customHeight="1" hidden="1">
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" t="s" s="4">
         <v>12</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" ht="9" customHeight="1" hidden="1">
+    <row r="55" ht="16" customHeight="1">
       <c r="A55" t="s" s="4">
         <v>56</v>
       </c>
@@ -7661,7 +7661,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" ht="9" customHeight="1" hidden="1">
+    <row r="57" ht="16" customHeight="1">
       <c r="A57" t="s" s="4">
         <v>56</v>
       </c>
@@ -7733,7 +7733,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" ht="9" customHeight="1" hidden="1">
+    <row r="59" ht="16" customHeight="1">
       <c r="A59" t="s" s="4">
         <v>56</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" ht="9" customHeight="1" hidden="1">
+    <row r="60" ht="16" customHeight="1">
       <c r="A60" t="s" s="4">
         <v>56</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" ht="9" customHeight="1" hidden="1">
+    <row r="61" ht="16" customHeight="1">
       <c r="A61" t="s" s="4">
         <v>12</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" ht="9" customHeight="1" hidden="1">
+    <row r="62" ht="16" customHeight="1">
       <c r="A62" t="s" s="4">
         <v>12</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" ht="9" customHeight="1" hidden="1">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" t="s" s="4">
         <v>56</v>
       </c>
@@ -7991,7 +7991,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" ht="9" customHeight="1" hidden="1">
+    <row r="66" ht="16" customHeight="1">
       <c r="A66" t="s" s="4">
         <v>56</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" ht="9" customHeight="1" hidden="1">
+    <row r="67" ht="16" customHeight="1">
       <c r="A67" t="s" s="4">
         <v>12</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" ht="9" customHeight="1" hidden="1">
+    <row r="68" ht="16" customHeight="1">
       <c r="A68" t="s" s="4">
         <v>12</v>
       </c>
@@ -8139,7 +8139,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" ht="9" customHeight="1" hidden="1">
+    <row r="70" ht="16" customHeight="1">
       <c r="A70" t="s" s="4">
         <v>56</v>
       </c>
@@ -8211,7 +8211,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" ht="9" customHeight="1" hidden="1">
+    <row r="72" ht="16" customHeight="1">
       <c r="A72" t="s" s="4">
         <v>56</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" ht="9" customHeight="1" hidden="1">
+    <row r="73" ht="16" customHeight="1">
       <c r="A73" t="s" s="4">
         <v>12</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" ht="9" customHeight="1" hidden="1">
+    <row r="74" ht="16" customHeight="1">
       <c r="A74" t="s" s="4">
         <v>12</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="75" ht="9" customHeight="1" hidden="1">
+    <row r="75" ht="16" customHeight="1">
       <c r="A75" t="s" s="4">
         <v>12</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="76" ht="9" customHeight="1" hidden="1">
+    <row r="76" ht="16" customHeight="1">
       <c r="A76" t="s" s="4">
         <v>12</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="77" ht="9" customHeight="1" hidden="1">
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" t="s" s="4">
         <v>12</v>
       </c>
@@ -8473,7 +8473,7 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
     </row>
-    <row r="79" ht="9" customHeight="1" hidden="1">
+    <row r="79" ht="16" customHeight="1">
       <c r="A79" t="s" s="4">
         <v>34</v>
       </c>
@@ -8613,7 +8613,7 @@
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
     </row>
-    <row r="83" ht="9" customHeight="1" hidden="1">
+    <row r="83" ht="16" customHeight="1">
       <c r="A83" t="s" s="4">
         <v>12</v>
       </c>
@@ -8719,7 +8719,7 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
     </row>
-    <row r="86" ht="9" customHeight="1" hidden="1">
+    <row r="86" ht="16" customHeight="1">
       <c r="A86" t="s" s="4">
         <v>56</v>
       </c>
@@ -8859,7 +8859,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
     </row>
-    <row r="90" ht="9" customHeight="1" hidden="1">
+    <row r="90" ht="16" customHeight="1">
       <c r="A90" t="s" s="4">
         <v>12</v>
       </c>
@@ -8897,7 +8897,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="91" ht="9" customHeight="1" hidden="1">
+    <row r="91" ht="16" customHeight="1">
       <c r="A91" t="s" s="4">
         <v>12</v>
       </c>
@@ -9105,7 +9105,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
     </row>
-    <row r="97" ht="9" customHeight="1" hidden="1">
+    <row r="97" ht="16" customHeight="1">
       <c r="A97" t="s" s="4">
         <v>12</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
-    <row r="101" ht="9" customHeight="1" hidden="1">
+    <row r="101" ht="16" customHeight="1">
       <c r="A101" t="s" s="4">
         <v>12</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="102" ht="9" customHeight="1" hidden="1">
+    <row r="102" ht="16" customHeight="1">
       <c r="A102" t="s" s="4">
         <v>12</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="103" ht="9" customHeight="1" hidden="1">
+    <row r="103" ht="16" customHeight="1">
       <c r="A103" t="s" s="4">
         <v>12</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="104" ht="9" customHeight="1" hidden="1">
+    <row r="104" ht="16" customHeight="1">
       <c r="A104" t="s" s="4">
         <v>12</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="105" ht="9" customHeight="1" hidden="1">
+    <row r="105" ht="16" customHeight="1">
       <c r="A105" t="s" s="4">
         <v>12</v>
       </c>
@@ -9469,7 +9469,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
     </row>
-    <row r="107" ht="9" customHeight="1" hidden="1">
+    <row r="107" ht="16" customHeight="1">
       <c r="A107" t="s" s="4">
         <v>12</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="108" ht="9" customHeight="1" hidden="1">
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" t="s" s="4">
         <v>12</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" ht="9" customHeight="1" hidden="1">
+    <row r="109" ht="16" customHeight="1">
       <c r="A109" t="s" s="4">
         <v>12</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" ht="9" customHeight="1" hidden="1">
+    <row r="110" ht="16" customHeight="1">
       <c r="A110" t="s" s="4">
         <v>12</v>
       </c>
@@ -9757,7 +9757,7 @@
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
     </row>
-    <row r="115" ht="9" customHeight="1" hidden="1">
+    <row r="115" ht="16" customHeight="1">
       <c r="A115" t="s" s="4">
         <v>12</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="116" ht="9" customHeight="1" hidden="1">
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" t="s" s="4">
         <v>12</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="117" ht="9" customHeight="1" hidden="1">
+    <row r="117" ht="16" customHeight="1">
       <c r="A117" t="s" s="4">
         <v>12</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" ht="9" customHeight="1" hidden="1">
+    <row r="118" ht="16" customHeight="1">
       <c r="A118" t="s" s="4">
         <v>12</v>
       </c>
@@ -9943,7 +9943,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
     </row>
-    <row r="120" ht="9" customHeight="1" hidden="1">
+    <row r="120" ht="16" customHeight="1">
       <c r="A120" t="s" s="4">
         <v>12</v>
       </c>
@@ -10049,7 +10049,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
     </row>
-    <row r="123" ht="9" customHeight="1" hidden="1">
+    <row r="123" ht="16" customHeight="1">
       <c r="A123" t="s" s="4">
         <v>12</v>
       </c>
@@ -10359,7 +10359,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
     </row>
-    <row r="132" ht="9" customHeight="1" hidden="1">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" t="s" s="4">
         <v>12</v>
       </c>
@@ -10533,7 +10533,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
     </row>
-    <row r="137" ht="9" customHeight="1" hidden="1">
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" t="s" s="4">
         <v>34</v>
       </c>
@@ -10605,7 +10605,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
     </row>
-    <row r="139" ht="9" customHeight="1" hidden="1">
+    <row r="139" ht="16" customHeight="1">
       <c r="A139" t="s" s="4">
         <v>56</v>
       </c>
@@ -10813,7 +10813,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
     </row>
-    <row r="145" ht="9" customHeight="1" hidden="1">
+    <row r="145" ht="16" customHeight="1">
       <c r="A145" t="s" s="4">
         <v>12</v>
       </c>
@@ -10919,7 +10919,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
     </row>
-    <row r="148" ht="9" customHeight="1" hidden="1">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" t="s" s="4">
         <v>56</v>
       </c>
@@ -11365,7 +11365,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
     </row>
-    <row r="161" ht="9" customHeight="1" hidden="1">
+    <row r="161" ht="16" customHeight="1">
       <c r="A161" t="s" s="4">
         <v>12</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="162" ht="9" customHeight="1" hidden="1">
+    <row r="162" ht="16" customHeight="1">
       <c r="A162" t="s" s="4">
         <v>12</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="163" ht="9" customHeight="1" hidden="1">
+    <row r="163" ht="16" customHeight="1">
       <c r="A163" t="s" s="4">
         <v>12</v>
       </c>
@@ -11751,7 +11751,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
     </row>
-    <row r="172" ht="9" customHeight="1" hidden="1">
+    <row r="172" ht="16" customHeight="1">
       <c r="A172" t="s" s="4">
         <v>12</v>
       </c>
@@ -11891,7 +11891,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
     </row>
-    <row r="176" ht="9" customHeight="1" hidden="1">
+    <row r="176" ht="16" customHeight="1">
       <c r="A176" t="s" s="4">
         <v>12</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="177" ht="9" customHeight="1" hidden="1">
+    <row r="177" ht="16" customHeight="1">
       <c r="A177" t="s" s="4">
         <v>56</v>
       </c>
@@ -12137,7 +12137,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" ht="9" customHeight="1" hidden="1">
+    <row r="183" ht="16" customHeight="1">
       <c r="A183" t="s" s="4">
         <v>12</v>
       </c>
@@ -12685,7 +12685,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
     </row>
-    <row r="199" ht="9" customHeight="1" hidden="1">
+    <row r="199" ht="16" customHeight="1">
       <c r="A199" t="s" s="4">
         <v>12</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="200" ht="9" customHeight="1" hidden="1">
+    <row r="200" ht="16" customHeight="1">
       <c r="A200" t="s" s="4">
         <v>12</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="201" ht="9" customHeight="1" hidden="1">
+    <row r="201" ht="16" customHeight="1">
       <c r="A201" t="s" s="4">
         <v>12</v>
       </c>
@@ -12833,7 +12833,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
     </row>
-    <row r="203" ht="9" customHeight="1" hidden="1">
+    <row r="203" ht="16" customHeight="1">
       <c r="A203" t="s" s="4">
         <v>34</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" ht="9" customHeight="1" hidden="1">
+    <row r="204" ht="16" customHeight="1">
       <c r="A204" t="s" s="4">
         <v>34</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" ht="9" customHeight="1" hidden="1">
+    <row r="205" ht="16" customHeight="1">
       <c r="A205" t="s" s="4">
         <v>34</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" ht="9" customHeight="1" hidden="1">
+    <row r="206" ht="16" customHeight="1">
       <c r="A206" t="s" s="4">
         <v>34</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" ht="9" customHeight="1" hidden="1">
+    <row r="207" ht="16" customHeight="1">
       <c r="A207" t="s" s="4">
         <v>34</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" ht="9" customHeight="1" hidden="1">
+    <row r="208" ht="16" customHeight="1">
       <c r="A208" t="s" s="4">
         <v>34</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="209" ht="9" customHeight="1" hidden="1">
+    <row r="209" ht="16" customHeight="1">
       <c r="A209" t="s" s="4">
         <v>34</v>
       </c>
@@ -13235,7 +13235,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
     </row>
-    <row r="214" ht="9" customHeight="1" hidden="1">
+    <row r="214" ht="16" customHeight="1">
       <c r="A214" t="s" s="4">
         <v>34</v>
       </c>
@@ -13273,7 +13273,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="215" ht="9" customHeight="1" hidden="1">
+    <row r="215" ht="16" customHeight="1">
       <c r="A215" t="s" s="4">
         <v>34</v>
       </c>
@@ -13685,7 +13685,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
     </row>
-    <row r="227" ht="9" customHeight="1" hidden="1">
+    <row r="227" ht="16" customHeight="1">
       <c r="A227" t="s" s="4">
         <v>12</v>
       </c>
@@ -14199,7 +14199,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
     </row>
-    <row r="242" ht="9" customHeight="1" hidden="1">
+    <row r="242" ht="16" customHeight="1">
       <c r="A242" t="s" s="4">
         <v>12</v>
       </c>
@@ -14271,7 +14271,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
     </row>
-    <row r="244" ht="9" customHeight="1" hidden="1">
+    <row r="244" ht="16" customHeight="1">
       <c r="A244" t="s" s="4">
         <v>56</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="245" ht="9" customHeight="1" hidden="1">
+    <row r="245" ht="16" customHeight="1">
       <c r="A245" t="s" s="4">
         <v>12</v>
       </c>
@@ -14415,7 +14415,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
     </row>
-    <row r="248" ht="9" customHeight="1" hidden="1">
+    <row r="248" ht="16" customHeight="1">
       <c r="A248" t="s" s="4">
         <v>56</v>
       </c>
@@ -14589,7 +14589,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
     </row>
-    <row r="253" ht="9" customHeight="1" hidden="1">
+    <row r="253" ht="16" customHeight="1">
       <c r="A253" t="s" s="4">
         <v>56</v>
       </c>
@@ -14797,7 +14797,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
     </row>
-    <row r="259" ht="9" customHeight="1" hidden="1">
+    <row r="259" ht="16" customHeight="1">
       <c r="A259" t="s" s="4">
         <v>56</v>
       </c>
@@ -15651,7 +15651,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
     </row>
-    <row r="284" ht="9" customHeight="1" hidden="1">
+    <row r="284" ht="16" customHeight="1">
       <c r="A284" t="s" s="4">
         <v>12</v>
       </c>
@@ -15689,7 +15689,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="285" ht="9" customHeight="1" hidden="1">
+    <row r="285" ht="16" customHeight="1">
       <c r="A285" t="s" s="4">
         <v>12</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="286" ht="9" customHeight="1" hidden="1">
+    <row r="286" ht="16" customHeight="1">
       <c r="A286" t="s" s="4">
         <v>12</v>
       </c>
@@ -15799,7 +15799,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
     </row>
-    <row r="288" ht="9" customHeight="1" hidden="1">
+    <row r="288" ht="16" customHeight="1">
       <c r="A288" t="s" s="4">
         <v>12</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="289" ht="9" customHeight="1" hidden="1">
+    <row r="289" ht="16" customHeight="1">
       <c r="A289" t="s" s="4">
         <v>12</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="290" ht="9" customHeight="1" hidden="1">
+    <row r="290" ht="16" customHeight="1">
       <c r="A290" t="s" s="4">
         <v>12</v>
       </c>
@@ -15981,7 +15981,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
     </row>
-    <row r="293" ht="9" customHeight="1" hidden="1">
+    <row r="293" ht="16" customHeight="1">
       <c r="A293" t="s" s="4">
         <v>34</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" ht="9" customHeight="1" hidden="1">
+    <row r="294" ht="16" customHeight="1">
       <c r="A294" t="s" s="4">
         <v>34</v>
       </c>
@@ -16567,7 +16567,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
     </row>
-    <row r="310" ht="9" customHeight="1" hidden="1">
+    <row r="310" ht="16" customHeight="1">
       <c r="A310" t="s" s="4">
         <v>12</v>
       </c>
@@ -16775,7 +16775,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
     </row>
-    <row r="316" ht="9" customHeight="1" hidden="1">
+    <row r="316" ht="16" customHeight="1">
       <c r="A316" t="s" s="4">
         <v>12</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="317" ht="9" customHeight="1" hidden="1">
+    <row r="317" ht="16" customHeight="1">
       <c r="A317" t="s" s="4">
         <v>12</v>
       </c>
@@ -16885,7 +16885,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
     </row>
-    <row r="319" ht="9" customHeight="1" hidden="1">
+    <row r="319" ht="16" customHeight="1">
       <c r="A319" t="s" s="4">
         <v>56</v>
       </c>
@@ -17637,7 +17637,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
     </row>
-    <row r="341" ht="9" customHeight="1" hidden="1">
+    <row r="341" ht="16" customHeight="1">
       <c r="A341" t="s" s="4">
         <v>12</v>
       </c>
@@ -17845,7 +17845,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
     </row>
-    <row r="347" ht="9" customHeight="1" hidden="1">
+    <row r="347" ht="16" customHeight="1">
       <c r="A347" t="s" s="4">
         <v>12</v>
       </c>
@@ -17917,7 +17917,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
     </row>
-    <row r="349" ht="9" customHeight="1" hidden="1">
+    <row r="349" ht="16" customHeight="1">
       <c r="A349" t="s" s="4">
         <v>12</v>
       </c>
